--- a/data/trans_camb/IP2001-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.719024402119879</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-10.15719069168021</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.286275222653426</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.18930402871494</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.6645971585535648</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-10.15504726575696</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-7.088824679837325</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-15.08608202650551</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.153775629256773</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-14.98345425843599</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.293743975107462</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-13.61476077222417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.720485512990947</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-2.862582060880586</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.470106826061526</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-4.412857332142288</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4.268704486054261</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-5.079336405391449</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.1140637391873963</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.6739678322795947</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.2335401651504519</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.7241060423761133</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04556399169538374</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.6962179770527667</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.3952842507542476</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.8948546530932506</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.1348147593667484</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.9009366499899313</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1969201797872389</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8486199005528096</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.3031378413645088</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.1472215825229735</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.7564992062138275</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.3271413102560368</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3290375479303928</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.3700514954900296</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1.418075287153145</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.58807019593693</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9924221582419026</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.653113315208172</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2196244031774403</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-4.073407248427127</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.876814064600542</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.547661206671629</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.399550457657183</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.910675438438551</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.009116903320688</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-6.794975686046937</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>6.217727619771867</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.020484775623659</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.169224142225521</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-2.163469038767332</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.470503547733253</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.198023087669736</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.2062910889623215</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3764932820334102</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1177941689326607</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6709884289834561</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.028722932107208</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.532728595496985</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3287032203607129</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.715379246384218</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.5115926802963409</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8733035352675437</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3277184611717778</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7301907989969513</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.280999706498423</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2583733972594927</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.4935817461859853</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.2698353578771491</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5738022990058995</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.1942867147300939</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.3450440205815739</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-3.579745692187411</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.198979612899424</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.5963122686099234</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.827849868247106</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.164261909455691</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-5.805785802768815</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.938030790953352</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.585737375487925</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.222703086748636</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-4.094455981638863</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-5.67538306391105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.32284673214154</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4293679818337366</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.069439717915539</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.580919015688374</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.379274571650726</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.9541922415808081</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.04441471349507417</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.4607915796823417</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.2033264725057403</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.1011243800844526</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1207206175524956</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3156019518467174</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.5674486093268664</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8077866228361701</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7006979817666328</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.5930910482538021</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4745802038951334</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6243987465808891</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.8094811269189029</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.1202816683578066</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.9479418930805975</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.05894474057769</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.4691584781143964</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2043009843151663</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.293948240831287</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>6.965246970469702</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.216053161709325</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.711425853489453</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.8300178710945926</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4.844396880560849</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.57849301940071</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.057467974035831</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.439146945778577</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.924271268257521</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.152736855134775</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.7137173445597333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>4.917756756650165</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>12.97919593397601</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>8.101629613449175</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>7.309753083483099</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.524836369756098</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>8.613831892993749</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.06007641612169756</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.423539988553634</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.5507366844195811</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.6738474105235318</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1845818452320204</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.07731140062195</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.730854906758841</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.03827145858374542</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.6228461157080161</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4928418800717517</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5328831714949351</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.03745518073730461</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>2.309355175910067</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>5.598162114485334</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>5.883777362843329</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>5.626351324694753</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.678506458156153</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3.177977797837932</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.0210992782306435</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-3.651374143116216</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.170750946990885</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-4.624890474741142</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.5563557333939164</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-4.102825634566665</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-2.715967255661802</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-6.184076113122961</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.385821830510406</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-6.927024575250155</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.387298786727996</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-6.064104557463123</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>2.536134683078641</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-1.275866159713052</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3.875431944593069</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-2.245007866337918</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2.360998590961409</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-2.474385242872761</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.002191306541314071</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.3792205570792929</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.1261089065552144</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.4981758778041567</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.05880504297558353</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.433655704939405</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.2445822062862046</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5549677316266517</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.1284168891133857</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.6507889276534414</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.1286400144766903</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.5720854978492</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.3016885317307396</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.1498460492024463</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.511144603733663</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.2614872757146222</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2880728978754888</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.286308110133963</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
